--- a/calificaciones/P00-S02-corte-07sep.xlsx
+++ b/calificaciones/P00-S02-corte-07sep.xlsx
@@ -641,6 +641,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -2756,6 +2757,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
@@ -2851,6 +2853,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -2875,6 +2878,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -2970,6 +2974,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -3006,6 +3011,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
@@ -3101,6 +3107,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -3137,6 +3144,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
@@ -3232,6 +3240,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -3268,6 +3277,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
@@ -3363,6 +3373,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -3390,7 +3401,7 @@
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Tu carpeta se llama Salgado_Roman con mayusculas.</t>
+          <t>Tu carpeta lleva mayusculas.</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
@@ -3399,6 +3410,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
@@ -3494,6 +3506,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -3542,6 +3555,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
@@ -3637,6 +3651,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -3685,6 +3700,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
@@ -3780,6 +3796,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -3804,6 +3821,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -3899,6 +3917,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -3923,6 +3942,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
